--- a/Stundenplan.xlsx
+++ b/Stundenplan.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2CB53732CD90A3B6/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2cb53732cd90a3b6/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{63AB0A45-4144-4C0D-8706-71CF7F37F95B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="14_{63AB0A45-4144-4C0D-8706-71CF7F37F95B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7D6412D-B28D-4C63-B32E-5573A267555C}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Wochenplan" sheetId="1" r:id="rId1"/>
@@ -121,9 +121,6 @@
 4490-P RUST (P, 1. PG) · Raum: C5-19</t>
   </si>
   <si>
-    <t>4030-P(PL) Algorithmen und Datenstrukturen (P, 1. PG) · Raum: C0-08</t>
-  </si>
-  <si>
     <t>4841 Fahrzeugelektronik (V, 1. PG) · Raum: C5-14
 2225 Software Engineering (Ü, 2. PG) · Raum: Digital, ExterneRäume
 2225 Software Engineering (Ü, 1. PG) · Raum: C5-07</t>
@@ -139,10 +136,6 @@
     <t>14:00–15:00</t>
   </si>
   <si>
-    <t>4030-P(PL) Algorithmen und Datenstrukturen (P, 1. PG) · Raum: C0-08
-4130-P-748 VHDL (P, 1. PG) · Raum: C5-11</t>
-  </si>
-  <si>
     <t>4845 Fahrzeugelektronik (Ü, 1. PG) · Raum: C6-10</t>
   </si>
   <si>
@@ -176,10 +169,6 @@
   </si>
   <si>
     <t>19:00–20:00</t>
-  </si>
-  <si>
-    <t>4150-P-748 Entwicklung nachhaltiger Elektrofahrzeuge (P, 1. PG) · Raum: D3-33
-1195 Programmieren in C (Ü, 1. PG) · Raum: C0-08</t>
   </si>
   <si>
     <t>Legende: P = Praktikum · V = Vorlesung · Ü = Übung · S = Seminar</t>
@@ -215,6 +204,18 @@
   <si>
     <t>4495 RUST (Ü, 1. PG) · Raum: C5-11
 2031 Algorithmen und Datenstrukturen (V, 1. PG) · Raum: H8</t>
+  </si>
+  <si>
+    <t>4030-P(PL) Algorithmen und Datenstrukturen (P, 1. PG) · Raum: C0-08
+4521 Sustainable, integrated vehicle-, charging- and storage systems (V, 1.PG) · Raum D3-12</t>
+  </si>
+  <si>
+    <t>4030-P(PL) Algorithmen und Datenstrukturen (P, 1. PG) · Raum: C0-08
+4130-P-748 VHDL (P, 1. PG) · Raum: C5-11
+4520 Sustainable, integrated vehicle-, charging- and storage systems (P, 1.PG) · Raum D3-12</t>
+  </si>
+  <si>
+    <t>1195 Programmieren in C (Ü, 1. PG) · Raum: C0-08</t>
   </si>
 </sst>
 </file>
@@ -617,7 +618,7 @@
     </row>
     <row r="2" spans="1:6" ht="17.55" customHeight="1">
       <c r="A2" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -736,18 +737,18 @@
         <v>26</v>
       </c>
       <c r="D9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="100.05" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>25</v>
@@ -756,96 +757,96 @@
         <v>26</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="100.05" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="100.05" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>32</v>
-      </c>
       <c r="E12" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="100.05" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F13" s="2"/>
     </row>
     <row r="14" spans="1:6" ht="100.05" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F14" s="2"/>
     </row>
     <row r="15" spans="1:6" ht="100.05" customHeight="1">
       <c r="A15" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
@@ -853,11 +854,11 @@
     </row>
     <row r="16" spans="1:6" ht="100.05" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="2" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
@@ -865,7 +866,7 @@
     </row>
     <row r="18" spans="1:6" ht="17.55" customHeight="1">
       <c r="A18" s="7" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -875,7 +876,7 @@
     </row>
     <row r="19" spans="1:6" ht="16.05" customHeight="1">
       <c r="A19" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>

--- a/Stundenplan.xlsx
+++ b/Stundenplan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2cb53732cd90a3b6/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="14_{63AB0A45-4144-4C0D-8706-71CF7F37F95B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7D6412D-B28D-4C63-B32E-5573A267555C}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="14_{63AB0A45-4144-4C0D-8706-71CF7F37F95B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{837523B4-F67E-4385-8DED-00BC5888948D}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -206,16 +206,16 @@
 2031 Algorithmen und Datenstrukturen (V, 1. PG) · Raum: H8</t>
   </si>
   <si>
-    <t>4030-P(PL) Algorithmen und Datenstrukturen (P, 1. PG) · Raum: C0-08
-4521 Sustainable, integrated vehicle-, charging- and storage systems (V, 1.PG) · Raum D3-12</t>
+    <t>1195 Programmieren in C (Ü, 1. PG) · Raum: C0-08</t>
   </si>
   <si>
     <t>4030-P(PL) Algorithmen und Datenstrukturen (P, 1. PG) · Raum: C0-08
 4130-P-748 VHDL (P, 1. PG) · Raum: C5-11
-4520 Sustainable, integrated vehicle-, charging- and storage systems (P, 1.PG) · Raum D3-12</t>
-  </si>
-  <si>
-    <t>1195 Programmieren in C (Ü, 1. PG) · Raum: C0-08</t>
+4520 Sustainable, integrated vehicle-, charging- and storage systems (P, 1.PG) · Raum: D3-12</t>
+  </si>
+  <si>
+    <t>4030-P(PL) Algorithmen und Datenstrukturen (P, 1. PG) · Raum: C0-08
+4521 Sustainable, integrated vehicle-, charging- and storage systems (V, 1.PG) · Raum: D3-12</t>
   </si>
 </sst>
 </file>
@@ -402,6 +402,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -737,7 +741,7 @@
         <v>26</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>45</v>
@@ -757,7 +761,7 @@
         <v>26</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>45</v>
@@ -858,7 +862,7 @@
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>

--- a/Stundenplan.xlsx
+++ b/Stundenplan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2cb53732cd90a3b6/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="14_{63AB0A45-4144-4C0D-8706-71CF7F37F95B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{837523B4-F67E-4385-8DED-00BC5888948D}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="14_{63AB0A45-4144-4C0D-8706-71CF7F37F95B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A97C8F7-8674-4540-B691-21FC1F9FE49A}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="54">
   <si>
     <t>Wochenplan – Bachelor Elektrotechnik (5. Fachsemester)</t>
   </si>
@@ -69,10 +69,6 @@
     <t>09:00–10:00</t>
   </si>
   <si>
-    <t>4161 Funkbetriebstechnik (V, 1. PG) · Raum: D3-33
-3061 Betriebsorganisation (V, 1. PG) · Raum: C1-08</t>
-  </si>
-  <si>
     <t>10:00–11:00</t>
   </si>
   <si>
@@ -85,11 +81,6 @@
 3011 Projektmanagement (V, 1. PG) · Raum: C7-09</t>
   </si>
   <si>
-    <t>3061 Betriebsorganisation (V, 1. PG) · Raum: C1-08
-2221 Software Engineering (V, 1. PG) · Raum: Digital, ExterneRäume
-4165 Funkbetriebstechnik (Ü, 1. PG) · Raum: D3-33</t>
-  </si>
-  <si>
     <t>11:00–12:00</t>
   </si>
   <si>
@@ -103,10 +94,6 @@
     <t>4861 English for academic writing: Ethics of AI (Ü, 1. PG) · Raum: D3-12
 3015 Projektmanagement (Ü, 2. PG) · Raum: C7-10
 3015 Projektmanagement (Ü, 1. PG) · Raum: C7-09</t>
-  </si>
-  <si>
-    <t>3061 Betriebsorganisation (V, 1. PG) · Raum: C1-08
-2221 Software Engineering (V, 1. PG) · Raum: Digital, ExterneRäume</t>
   </si>
   <si>
     <t>12:00–13:00</t>
@@ -210,12 +197,18 @@
   </si>
   <si>
     <t>4030-P(PL) Algorithmen und Datenstrukturen (P, 1. PG) · Raum: C0-08
-4130-P-748 VHDL (P, 1. PG) · Raum: C5-11
+4521 Sustainable, integrated vehicle-, charging- and storage systems (V, 1.PG) · Raum: D3-12</t>
+  </si>
+  <si>
+    <t>4030-P(PL) Algorithmen und Datenstrukturen (P, 1. PG) · Raum: C0-08
 4520 Sustainable, integrated vehicle-, charging- and storage systems (P, 1.PG) · Raum: D3-12</t>
   </si>
   <si>
-    <t>4030-P(PL) Algorithmen und Datenstrukturen (P, 1. PG) · Raum: C0-08
-4521 Sustainable, integrated vehicle-, charging- and storage systems (V, 1.PG) · Raum: D3-12</t>
+    <t>2221 Software Engineering (V, 1. PG) · Raum: Digital, ExterneRäume
+4165 Funkbetriebstechnik (Ü, 1. PG) · Raum: D3-33</t>
+  </si>
+  <si>
+    <t>2221 Software Engineering (V, 1. PG) · Raum: Digital, ExterneRäume</t>
   </si>
 </sst>
 </file>
@@ -622,7 +615,7 @@
     </row>
     <row r="2" spans="1:6" ht="17.55" customHeight="1">
       <c r="A2" s="6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -687,12 +680,12 @@
         <v>11</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="100.05" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>8</v>
@@ -701,156 +694,156 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="F7" s="2" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="100.05" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="F8" s="2" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="100.05" customHeight="1">
       <c r="A9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="100.05" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="100.05" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="E11" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="100.05" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="100.05" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F13" s="2"/>
     </row>
     <row r="14" spans="1:6" ht="100.05" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F14" s="2"/>
     </row>
     <row r="15" spans="1:6" ht="100.05" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
@@ -858,11 +851,11 @@
     </row>
     <row r="16" spans="1:6" ht="100.05" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
@@ -870,7 +863,7 @@
     </row>
     <row r="18" spans="1:6" ht="17.55" customHeight="1">
       <c r="A18" s="7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -880,7 +873,7 @@
     </row>
     <row r="19" spans="1:6" ht="16.05" customHeight="1">
       <c r="A19" s="8" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>

--- a/Stundenplan.xlsx
+++ b/Stundenplan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2cb53732cd90a3b6/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="14_{63AB0A45-4144-4C0D-8706-71CF7F37F95B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A97C8F7-8674-4540-B691-21FC1F9FE49A}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="14_{63AB0A45-4144-4C0D-8706-71CF7F37F95B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F3AC68EE-4137-421C-9D10-034954BE3921}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -103,11 +103,6 @@
 4280-P-748 Programmieren in C (P, 1. PG) · Raum: C5-11</t>
   </si>
   <si>
-    <t>4040-P-748 Betriebssysteme (P, 1. PG) · Raum: C6-05
-4160-P-748 Funkbetriebstechnik (P, 1. PG) · Raum: C4-19
-4490-P RUST (P, 1. PG) · Raum: C5-19</t>
-  </si>
-  <si>
     <t>4841 Fahrzeugelektronik (V, 1. PG) · Raum: C5-14
 2225 Software Engineering (Ü, 2. PG) · Raum: Digital, ExterneRäume
 2225 Software Engineering (Ü, 1. PG) · Raum: C5-07</t>
@@ -209,6 +204,10 @@
   </si>
   <si>
     <t>2221 Software Engineering (V, 1. PG) · Raum: Digital, ExterneRäume</t>
+  </si>
+  <si>
+    <t>4040-P-748 Betriebssysteme (P, 1. PG) · Raum: C6-05
+4160-P-748 Funkbetriebstechnik (P, 1. PG) · Raum: C4-19</t>
   </si>
 </sst>
 </file>
@@ -615,7 +614,7 @@
     </row>
     <row r="2" spans="1:6" ht="17.55" customHeight="1">
       <c r="A2" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -700,7 +699,7 @@
         <v>16</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="100.05" customHeight="1">
@@ -720,7 +719,7 @@
         <v>20</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="100.05" customHeight="1">
@@ -731,119 +730,119 @@
         <v>22</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="100.05" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="100.05" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="100.05" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="100.05" customHeight="1">
       <c r="A13" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>32</v>
-      </c>
       <c r="C13" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F13" s="2"/>
     </row>
     <row r="14" spans="1:6" ht="100.05" customHeight="1">
       <c r="A14" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F14" s="2"/>
     </row>
     <row r="15" spans="1:6" ht="100.05" customHeight="1">
       <c r="A15" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="C15" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>37</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
@@ -851,11 +850,11 @@
     </row>
     <row r="16" spans="1:6" ht="100.05" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
@@ -863,7 +862,7 @@
     </row>
     <row r="18" spans="1:6" ht="17.55" customHeight="1">
       <c r="A18" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -873,7 +872,7 @@
     </row>
     <row r="19" spans="1:6" ht="16.05" customHeight="1">
       <c r="A19" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>

--- a/Stundenplan.xlsx
+++ b/Stundenplan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2cb53732cd90a3b6/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="14_{63AB0A45-4144-4C0D-8706-71CF7F37F95B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F3AC68EE-4137-421C-9D10-034954BE3921}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="14_{63AB0A45-4144-4C0D-8706-71CF7F37F95B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71CDEA3F-8F92-4222-8531-3214CBFEE1F1}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Wochenplan" sheetId="1" r:id="rId1"/>
@@ -50,10 +50,6 @@
 4471 Statistik für Ingenieurwissenschaften (V, 1. PG) · Raum: C1-08</t>
   </si>
   <si>
-    <t>4050-P-748 Webtechnologien 1 (P, 1. PG) · Raum: C6-05
-3071 Windenergie (V, 1. PG) · Raum: C5-14</t>
-  </si>
-  <si>
     <t>4851 Steuerungstechnik (V, 1. PG) · Raum: D3-12
 2041 Webtechnologien 1 (V, 1. PG) · Raum: H8</t>
   </si>
@@ -82,10 +78,6 @@
   </si>
   <si>
     <t>11:00–12:00</t>
-  </si>
-  <si>
-    <t>4050-P-748 Webtechnologien 1 (P, 1. PG) · Raum: C6-05
-3075 Windenergie (Ü, 1. PG) · Raum: C5-14</t>
   </si>
   <si>
     <t>2045 Webtechnologien 1 (Ü, 1. PG) · Raum: C0-08</t>
@@ -206,8 +198,13 @@
     <t>2221 Software Engineering (V, 1. PG) · Raum: Digital, ExterneRäume</t>
   </si>
   <si>
-    <t>4040-P-748 Betriebssysteme (P, 1. PG) · Raum: C6-05
-4160-P-748 Funkbetriebstechnik (P, 1. PG) · Raum: C4-19</t>
+    <t>3071 Windenergie (V, 1. PG) · Raum: C5-14</t>
+  </si>
+  <si>
+    <t>3075 Windenergie (Ü, 1. PG) · Raum: C5-14</t>
+  </si>
+  <si>
+    <t>4160-P-748 Funkbetriebstechnik (P, 1. PG) · Raum: C4-19</t>
   </si>
 </sst>
 </file>
@@ -614,7 +611,7 @@
     </row>
     <row r="2" spans="1:6" ht="17.55" customHeight="1">
       <c r="A2" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -650,199 +647,199 @@
         <v>8</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="100.05" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="100.05" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="F7" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="100.05" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="F8" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="100.05" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>53</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="100.05" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>53</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="100.05" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="100.05" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="100.05" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F13" s="2"/>
     </row>
     <row r="14" spans="1:6" ht="100.05" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F14" s="2"/>
     </row>
     <row r="15" spans="1:6" ht="100.05" customHeight="1">
       <c r="A15" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
@@ -850,11 +847,11 @@
     </row>
     <row r="16" spans="1:6" ht="100.05" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
@@ -862,7 +859,7 @@
     </row>
     <row r="18" spans="1:6" ht="17.55" customHeight="1">
       <c r="A18" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -872,7 +869,7 @@
     </row>
     <row r="19" spans="1:6" ht="16.05" customHeight="1">
       <c r="A19" s="8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>

--- a/Stundenplan.xlsx
+++ b/Stundenplan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2cb53732cd90a3b6/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="14_{63AB0A45-4144-4C0D-8706-71CF7F37F95B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71CDEA3F-8F92-4222-8531-3214CBFEE1F1}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="14_{63AB0A45-4144-4C0D-8706-71CF7F37F95B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3EA0EEAB-03D6-4E07-B217-292CE94FDFF8}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Wochenplan" sheetId="1" r:id="rId1"/>
@@ -54,11 +54,6 @@
 2041 Webtechnologien 1 (V, 1. PG) · Raum: H8</t>
   </si>
   <si>
-    <t>4860 English for academic writing: Ethics of AI (V, 1. PG) · Raum: D3-12
-3011 Projektmanagement (V, 2. PG) · Raum: C7-10
-3011 Projektmanagement (V, 1. PG) · Raum: C7-09</t>
-  </si>
-  <si>
     <t>4161 Funkbetriebstechnik (V, 1. PG) · Raum: D3-33</t>
   </si>
   <si>
@@ -72,20 +67,10 @@
 2045 Webtechnologien 1 (Ü, 1. PG) · Raum: C0-08</t>
   </si>
   <si>
-    <t>4861 English for academic writing: Ethics of AI (Ü, 1. PG) · Raum: D3-12
-3011 Projektmanagement (V, 2. PG) · Raum: C7-10
-3011 Projektmanagement (V, 1. PG) · Raum: C7-09</t>
-  </si>
-  <si>
     <t>11:00–12:00</t>
   </si>
   <si>
     <t>2045 Webtechnologien 1 (Ü, 1. PG) · Raum: C0-08</t>
-  </si>
-  <si>
-    <t>4861 English for academic writing: Ethics of AI (Ü, 1. PG) · Raum: D3-12
-3015 Projektmanagement (Ü, 2. PG) · Raum: C7-10
-3015 Projektmanagement (Ü, 1. PG) · Raum: C7-09</t>
   </si>
   <si>
     <t>12:00–13:00</t>
@@ -205,6 +190,18 @@
   </si>
   <si>
     <t>4160-P-748 Funkbetriebstechnik (P, 1. PG) · Raum: C4-19</t>
+  </si>
+  <si>
+    <t>4860 English for academic writing: Ethics of AI (V, 1. PG) · Raum: D3-12
+3011 Projektmanagement (V, 1. PG) · Raum: C7-09</t>
+  </si>
+  <si>
+    <t>4861 English for academic writing: Ethics of AI (Ü, 1. PG) · Raum: D3-12
+3011 Projektmanagement (V, 1. PG) · Raum: C7-09</t>
+  </si>
+  <si>
+    <t>4861 English for academic writing: Ethics of AI (Ü, 1. PG) · Raum: D3-12
+3015 Projektmanagement (Ü, 1. PG) · Raum: C7-09</t>
   </si>
 </sst>
 </file>
@@ -611,7 +608,7 @@
     </row>
     <row r="2" spans="1:6" ht="17.55" customHeight="1">
       <c r="A2" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -647,199 +644,199 @@
         <v>8</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="100.05" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="100.05" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="100.05" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="100.05" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="100.05" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="100.05" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="E11" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="100.05" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="100.05" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F13" s="2"/>
     </row>
     <row r="14" spans="1:6" ht="100.05" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F14" s="2"/>
     </row>
     <row r="15" spans="1:6" ht="100.05" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
@@ -847,11 +844,11 @@
     </row>
     <row r="16" spans="1:6" ht="100.05" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
@@ -859,7 +856,7 @@
     </row>
     <row r="18" spans="1:6" ht="17.55" customHeight="1">
       <c r="A18" s="7" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -869,7 +866,7 @@
     </row>
     <row r="19" spans="1:6" ht="16.05" customHeight="1">
       <c r="A19" s="8" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
